--- a/backend/uploads/Use cases/KWM/tasks_palazzo_albicocca_v2.xlsx
+++ b/backend/uploads/Use cases/KWM/tasks_palazzo_albicocca_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wu-my.sharepoint.com/personal/daniel_hoellmueller_wu_ac_at/Documents/Dokumente/AccountingBench/backend/uploads/Use cases/KWM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="128" documentId="11_5D41CD1A16E0D13891E2D9F0505ED87656CC8FBB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4E32EC9-87E4-4B33-A8F4-0C8B66EDB84E}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="11_5D41CD1A16E0D13891E2D9F0505ED87656CC8FBB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF1B3161-752B-4819-92A7-3EE64C23FEE7}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Questions" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="CIQWBGuid" hidden="1">"e0d8ae62-763e-4c8f-bed6-d3e7acdda44d"</definedName>
+    <definedName name="CIQWBGuid" hidden="1">"fc53528a-574b-4125-ae6c-bfbd0957fc06"</definedName>
     <definedName name="CIQWBInfo" hidden="1">"{ ""CIQVersion"":""9.49.2423.4439"" }"</definedName>
     <definedName name="IQ_CH">110000</definedName>
     <definedName name="IQ_CQ">5000</definedName>
